--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 PRONGHORN BUCK CWMU ANY LEGAL WEAPON.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 PRONGHORN BUCK CWMU ANY LEGAL WEAPON.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -649,7 +654,8 @@
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>1.7</t>
         </is>
@@ -717,8 +723,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>3.3</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
@@ -787,7 +798,8 @@
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -855,8 +867,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr"/>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -925,7 +942,8 @@
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
@@ -994,7 +1012,8 @@
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -1055,7 +1074,8 @@
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1124,7 +1144,8 @@
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1192,8 +1213,13 @@
           <t>40</t>
         </is>
       </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -1262,7 +1288,8 @@
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
@@ -1331,7 +1358,8 @@
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1400,7 +1428,8 @@
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr"/>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>1.6</t>
         </is>
@@ -1468,8 +1497,13 @@
           <t>83.3</t>
         </is>
       </c>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>2.4</t>
         </is>
@@ -1538,7 +1572,8 @@
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
@@ -1607,7 +1642,8 @@
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -1675,8 +1711,13 @@
           <t>80</t>
         </is>
       </c>
-      <c r="N17" s="3" t="inlineStr"/>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -1745,7 +1786,8 @@
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -1813,8 +1855,13 @@
           <t>100</t>
         </is>
       </c>
-      <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>3.4</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -1883,7 +1930,8 @@
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr"/>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>2.6</t>
         </is>
@@ -1952,7 +2000,8 @@
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr"/>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
@@ -2021,7 +2070,8 @@
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr"/>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
